--- a/artfynd/A 60287-2022 artfynd.xlsx
+++ b/artfynd/A 60287-2022 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>117717958</v>
       </c>
       <c r="B3" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 60287-2022 artfynd.xlsx
+++ b/artfynd/A 60287-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,246 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118880592</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56243</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bäcken/trumman, Lindsbergsmyra, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>534416</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6830068</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118880217</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57385</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102626</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Törnskata</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lanius collurio</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gammåkrarna, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>534416</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6830186</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60287-2022 artfynd.xlsx
+++ b/artfynd/A 60287-2022 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118880592</v>
+        <v>118880217</v>
       </c>
       <c r="B4" t="n">
-        <v>56243</v>
+        <v>57385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208257</v>
+        <v>102626</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,29 +955,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäcken/trumman, Lindsbergsmyra, Hls</t>
+          <t>Gammåkrarna, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>534416</v>
       </c>
       <c r="R4" t="n">
-        <v>6830068</v>
+        <v>6830186</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1004,12 +995,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,7 +1019,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118880217</v>
+        <v>118880592</v>
       </c>
       <c r="B5" t="n">
-        <v>57385</v>
+        <v>56243</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102626</v>
+        <v>208257</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1075,20 +1075,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammåkrarna, Hls</t>
+          <t>Bäcken/trumman, Lindsbergsmyra, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>534416</v>
       </c>
       <c r="R5" t="n">
-        <v>6830186</v>
+        <v>6830068</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1115,22 +1124,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,6 +1138,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60287-2022 artfynd.xlsx
+++ b/artfynd/A 60287-2022 artfynd.xlsx
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118880217</v>
+        <v>118880592</v>
       </c>
       <c r="B4" t="n">
-        <v>57385</v>
+        <v>56243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,16 +933,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102626</v>
+        <v>208257</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,20 +955,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammåkrarna, Hls</t>
+          <t>Bäcken/trumman, Lindsbergsmyra, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>534416</v>
       </c>
       <c r="R4" t="n">
-        <v>6830186</v>
+        <v>6830068</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -995,22 +1004,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,6 +1018,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118880592</v>
+        <v>118880217</v>
       </c>
       <c r="B5" t="n">
-        <v>56243</v>
+        <v>57385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208257</v>
+        <v>102626</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1075,29 +1075,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bäcken/trumman, Lindsbergsmyra, Hls</t>
+          <t>Gammåkrarna, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>534416</v>
       </c>
       <c r="R5" t="n">
-        <v>6830068</v>
+        <v>6830186</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1124,12 +1115,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1139,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60287-2022 artfynd.xlsx
+++ b/artfynd/A 60287-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,6 +1155,130 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124703466</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56112</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bäcken/trumman, Lindsbergsmyra, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>534416</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6830068</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gustav Forsblom</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60287-2022 artfynd.xlsx
+++ b/artfynd/A 60287-2022 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>124703466</v>
       </c>
       <c r="B6" t="n">
-        <v>56112</v>
+        <v>56226</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 60287-2022 artfynd.xlsx
+++ b/artfynd/A 60287-2022 artfynd.xlsx
@@ -1284,7 +1284,7 @@
         <v>133269318</v>
       </c>
       <c r="B7" t="n">
-        <v>56522</v>
+        <v>56529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 60287-2022 artfynd.xlsx
+++ b/artfynd/A 60287-2022 artfynd.xlsx
@@ -1284,7 +1284,7 @@
         <v>133269318</v>
       </c>
       <c r="B7" t="n">
-        <v>56529</v>
+        <v>56539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
